--- a/DOCUMENTACAO/Tabela de Referência de Funções.xlsx
+++ b/DOCUMENTACAO/Tabela de Referência de Funções.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\xampp\htdocs\Projeto-Integrador\DOCUMENTACAO\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{40017AC2-8C04-4A86-A5EE-40D6CDC48E69}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{56054791-6E20-45AA-B391-F885E3BC97E1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{711F7A4A-9FF9-4B67-B6DD-6A7B6F3D80AC}"/>
   </bookViews>
@@ -48,9 +48,16 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="1" x14ac:knownFonts="1">
+  <fonts count="2" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
+      <color theme="1"/>
+      <name val="Aptos Narrow"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="26"/>
       <color theme="1"/>
       <name val="Aptos Narrow"/>
       <family val="2"/>
@@ -65,7 +72,7 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="1">
+  <borders count="2">
     <border>
       <left/>
       <right/>
@@ -73,12 +80,31 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left style="thick">
+        <color theme="3"/>
+      </left>
+      <right style="thick">
+        <color theme="3"/>
+      </right>
+      <top style="thick">
+        <color theme="3"/>
+      </top>
+      <bottom style="thick">
+        <color theme="3"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="1">
+  <cellXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -94,6 +120,61 @@
     </ext>
   </extLst>
 </styleSheet>
+</file>
+
+<file path=xl/drawings/drawing1.xml><?xml version="1.0" encoding="utf-8"?>
+<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>2</xdr:col>
+      <xdr:colOff>9525</xdr:colOff>
+      <xdr:row>0</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>5</xdr:col>
+      <xdr:colOff>133350</xdr:colOff>
+      <xdr:row>10</xdr:row>
+      <xdr:rowOff>28575</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="4" name="Imagem 3">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{C08B7AB1-D312-5A14-CC78-B93A5399D39C}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId1" cstate="print">
+          <a:extLst>
+            <a:ext uri="{28A0092B-C50C-407E-A947-70E740481C1C}">
+              <a14:useLocalDpi xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" val="0"/>
+            </a:ext>
+          </a:extLst>
+        </a:blip>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="1228725" y="0"/>
+          <a:ext cx="1952625" cy="1952625"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+</xdr:wsDr>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -413,15 +494,102 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D668B2EB-85A2-43EE-86C7-63B60DAA87D6}">
-  <dimension ref="D2"/>
+  <dimension ref="F1:N10"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="6" max="6" width="9.42578125" customWidth="1"/>
+  </cols>
   <sheetData>
-    <row r="2" spans="4:4" x14ac:dyDescent="0.25">
-      <c r="D2" t="s">
+    <row r="1" spans="6:14" ht="15.75" thickBot="1" x14ac:dyDescent="0.3"/>
+    <row r="2" spans="6:14" ht="15" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="F2" s="2" t="s">
         <v>0</v>
       </c>
-    </row>
+      <c r="G2" s="2"/>
+      <c r="H2" s="2"/>
+      <c r="I2" s="2"/>
+      <c r="J2" s="2"/>
+      <c r="K2" s="2"/>
+      <c r="L2" s="2"/>
+      <c r="M2" s="2"/>
+    </row>
+    <row r="3" spans="6:14" ht="15" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="F3" s="2"/>
+      <c r="G3" s="2"/>
+      <c r="H3" s="2"/>
+      <c r="I3" s="2"/>
+      <c r="J3" s="2"/>
+      <c r="K3" s="2"/>
+      <c r="L3" s="2"/>
+      <c r="M3" s="2"/>
+    </row>
+    <row r="4" spans="6:14" ht="15" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="F4" s="2"/>
+      <c r="G4" s="2"/>
+      <c r="H4" s="2"/>
+      <c r="I4" s="2"/>
+      <c r="J4" s="2"/>
+      <c r="K4" s="2"/>
+      <c r="L4" s="2"/>
+      <c r="M4" s="2"/>
+    </row>
+    <row r="5" spans="6:14" ht="15" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="F5" s="2"/>
+      <c r="G5" s="2"/>
+      <c r="H5" s="2"/>
+      <c r="I5" s="2"/>
+      <c r="J5" s="2"/>
+      <c r="K5" s="2"/>
+      <c r="L5" s="2"/>
+      <c r="M5" s="2"/>
+      <c r="N5" s="1"/>
+    </row>
+    <row r="6" spans="6:14" ht="15" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="F6" s="2"/>
+      <c r="G6" s="2"/>
+      <c r="H6" s="2"/>
+      <c r="I6" s="2"/>
+      <c r="J6" s="2"/>
+      <c r="K6" s="2"/>
+      <c r="L6" s="2"/>
+      <c r="M6" s="2"/>
+    </row>
+    <row r="7" spans="6:14" ht="15" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="F7" s="2"/>
+      <c r="G7" s="2"/>
+      <c r="H7" s="2"/>
+      <c r="I7" s="2"/>
+      <c r="J7" s="2"/>
+      <c r="K7" s="2"/>
+      <c r="L7" s="2"/>
+      <c r="M7" s="2"/>
+    </row>
+    <row r="8" spans="6:14" ht="15" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="F8" s="2"/>
+      <c r="G8" s="2"/>
+      <c r="H8" s="2"/>
+      <c r="I8" s="2"/>
+      <c r="J8" s="2"/>
+      <c r="K8" s="2"/>
+      <c r="L8" s="2"/>
+      <c r="M8" s="2"/>
+    </row>
+    <row r="9" spans="6:14" ht="15" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="F9" s="2"/>
+      <c r="G9" s="2"/>
+      <c r="H9" s="2"/>
+      <c r="I9" s="2"/>
+      <c r="J9" s="2"/>
+      <c r="K9" s="2"/>
+      <c r="L9" s="2"/>
+      <c r="M9" s="2"/>
+    </row>
+    <row r="10" spans="6:14" ht="15.75" thickTop="1" x14ac:dyDescent="0.25"/>
   </sheetData>
+  <mergeCells count="1">
+    <mergeCell ref="F2:M9"/>
+  </mergeCells>
   <pageMargins left="0.511811024" right="0.511811024" top="0.78740157499999996" bottom="0.78740157499999996" header="0.31496062000000002" footer="0.31496062000000002"/>
+  <drawing r:id="rId1"/>
 </worksheet>
 </file>